--- a/src/bible.xlsx
+++ b/src/bible.xlsx
@@ -3356,7 +3356,7 @@
         <v>650</v>
       </c>
       <c r="C50" s="53">
-        <v>1400</v>
+        <v>140</v>
       </c>
       <c r="D50" s="54">
         <v>0.6</v>
